--- a/artfynd/A 48479-2023 artfynd.xlsx
+++ b/artfynd/A 48479-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48479-2023 artfynd.xlsx
+++ b/artfynd/A 48479-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62025693</v>
+        <v>62025694</v>
       </c>
       <c r="B2" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229748</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545859.2675617817</v>
+        <v>545795</v>
       </c>
       <c r="R2" t="n">
-        <v>6982447.404543645</v>
+        <v>6982480</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-10-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62025691</v>
+        <v>62025692</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545704.6759480583</v>
+        <v>545859</v>
       </c>
       <c r="R3" t="n">
-        <v>6982361.071821015</v>
+        <v>6982447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2016-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +866,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Bergsbrant</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Grov asp</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62025692</v>
+        <v>62025691</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545859.2675617817</v>
+        <v>545705</v>
       </c>
       <c r="R4" t="n">
-        <v>6982447.404543645</v>
+        <v>6982361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +957,9 @@
           <t>2016-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,12 +973,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Bergsbrant</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Grov asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62025694</v>
+        <v>62025693</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>229748</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545795.029083746</v>
+        <v>545859</v>
       </c>
       <c r="R5" t="n">
-        <v>6982480.166265856</v>
+        <v>6982447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1064,9 @@
           <t>2016-10-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-10-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1085,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 48479-2023 artfynd.xlsx
+++ b/artfynd/A 48479-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025692</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025691</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025693</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>